--- a/output/yearly_benthic_cover_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_49_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.49476907101443</v>
+        <v>45.85881456544389</v>
       </c>
       <c r="M2" t="n">
-        <v>99.72169541068143</v>
+        <v>99.45923692991565</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06133096653382</v>
+        <v>88.08764180500764</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96386379784656</v>
+        <v>45.9474759061165</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228791186067692</v>
+        <v>2.228871043394151</v>
       </c>
       <c r="E3" t="n">
-        <v>5.728221932198425</v>
+        <v>5.720412868079844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429303953558974</v>
+        <v>0.742957014464717</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98499586565145</v>
+        <v>33.97900847580858</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17479818637128</v>
+        <v>34.17602266537698</v>
       </c>
       <c r="I3" t="n">
-        <v>6.558278429914721</v>
+        <v>6.596888397478887</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643314970974359</v>
+        <v>4.643481340404481</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93866903346618</v>
+        <v>11.91235819499237</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8620650019554</v>
+        <v>48.90338635376561</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7645978332682</v>
+        <v>106.7632204548745</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15122079754694</v>
+        <v>87.26117723120441</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68570121444139</v>
+        <v>42.76101932759391</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184995438522645</v>
+        <v>2.189534899414106</v>
       </c>
       <c r="E4" t="n">
-        <v>6.528442380627939</v>
+        <v>6.537619008530484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444866145538831</v>
+        <v>0.7445204940876701</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31719068562578</v>
+        <v>33.37933126538182</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24638426947862</v>
+        <v>34.24794272803282</v>
       </c>
       <c r="I4" t="n">
-        <v>5.476680067776294</v>
+        <v>5.508975747709568</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653041340961769</v>
+        <v>4.653253088047938</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84877920245307</v>
+        <v>12.73882276879558</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28334518227457</v>
+        <v>44.31691100368053</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81782559916904</v>
+        <v>99.81675310007003</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.98624984869733</v>
+        <v>86.32647350652876</v>
       </c>
       <c r="C5" t="n">
-        <v>42.37079417989403</v>
+        <v>42.68143746325364</v>
       </c>
       <c r="D5" t="n">
-        <v>2.128198789835249</v>
+        <v>2.144732228976668</v>
       </c>
       <c r="E5" t="n">
-        <v>7.120740580410786</v>
+        <v>7.170339282983747</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458061218812236</v>
+        <v>0.7458426161555698</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45114550252833</v>
+        <v>32.69631717937427</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30708160653629</v>
+        <v>34.3087603431562</v>
       </c>
       <c r="I5" t="n">
-        <v>4.571988985747811</v>
+        <v>4.598965504909997</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661288261757647</v>
+        <v>4.661516350972311</v>
       </c>
       <c r="K5" t="n">
-        <v>14.01375015130266</v>
+        <v>13.67352649347123</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46332566692063</v>
+        <v>43.49200893917207</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84786999811733</v>
+        <v>99.84697289589694</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.62300983759553</v>
+        <v>85.08142631902373</v>
       </c>
       <c r="C6" t="n">
-        <v>41.71764945379653</v>
+        <v>42.15092932900049</v>
       </c>
       <c r="D6" t="n">
-        <v>2.061718859315653</v>
+        <v>2.084300623225189</v>
       </c>
       <c r="E6" t="n">
-        <v>7.534258262499137</v>
+        <v>7.608008074057117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469270878195863</v>
+        <v>0.7469641765471093</v>
       </c>
       <c r="G6" t="n">
-        <v>31.43744795294162</v>
+        <v>31.77504089014164</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35864603970097</v>
+        <v>34.36035212116702</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815717336446161</v>
+        <v>3.83823433046622</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668294298872414</v>
+        <v>4.668526103419434</v>
       </c>
       <c r="K6" t="n">
-        <v>15.37699016240447</v>
+        <v>14.91857368097628</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77836068975044</v>
+        <v>42.80274794822018</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87300030595144</v>
+        <v>99.87225095819694</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.03618565317304</v>
+        <v>83.72810402111571</v>
       </c>
       <c r="C7" t="n">
-        <v>40.72348871932658</v>
+        <v>41.3940795675167</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98452225207904</v>
+        <v>2.018848455351941</v>
       </c>
       <c r="E7" t="n">
-        <v>7.782792321709659</v>
+        <v>7.9028656916757</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478817269355302</v>
+        <v>0.7479165578832186</v>
       </c>
       <c r="G7" t="n">
-        <v>30.26034065182771</v>
+        <v>30.77722642549749</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40255943903439</v>
+        <v>34.40416166262805</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183828468239643</v>
+        <v>3.202606741309198</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674260793347064</v>
+        <v>4.674478486770117</v>
       </c>
       <c r="K7" t="n">
-        <v>16.96381434682696</v>
+        <v>16.27189597888427</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20670478561185</v>
+        <v>42.2274068333083</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89400785176539</v>
+        <v>99.89338237970928</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.92432402328423</v>
+        <v>88.61238352813714</v>
       </c>
       <c r="C8" t="n">
-        <v>43.05586439909592</v>
+        <v>43.72597735250569</v>
       </c>
       <c r="D8" t="n">
-        <v>1.988748067777119</v>
+        <v>2.023125816215859</v>
       </c>
       <c r="E8" t="n">
-        <v>9.634861835548922</v>
+        <v>9.755149324209778</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494742564920416</v>
+        <v>0.7495011785642238</v>
       </c>
       <c r="G8" t="n">
-        <v>30.77446283315222</v>
+        <v>31.29084383875877</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47581579863392</v>
+        <v>34.47705421395429</v>
       </c>
       <c r="I8" t="n">
-        <v>5.616747128604744</v>
+        <v>5.632326790407827</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68421410307526</v>
+        <v>4.6843823660264</v>
       </c>
       <c r="K8" t="n">
-        <v>12.07567597671577</v>
+        <v>11.38761647186286</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68163254703326</v>
+        <v>44.69905888446263</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81317292284494</v>
+        <v>99.81265270883117</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.82438860319625</v>
+        <v>86.82487682143591</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82771534074408</v>
+        <v>42.81338106082625</v>
       </c>
       <c r="D9" t="n">
-        <v>1.893689856872928</v>
+        <v>1.942660163645454</v>
       </c>
       <c r="E9" t="n">
-        <v>9.955859067211646</v>
+        <v>10.15083815588986</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750839212323653</v>
+        <v>0.7508541753608908</v>
       </c>
       <c r="G9" t="n">
-        <v>29.3035045826551</v>
+        <v>30.04631512542652</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53860376688804</v>
+        <v>34.53929206660097</v>
       </c>
       <c r="I9" t="n">
-        <v>4.689147040222041</v>
+        <v>4.702078538506639</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692745077022832</v>
+        <v>4.692838596005569</v>
       </c>
       <c r="K9" t="n">
-        <v>14.17561139680376</v>
+        <v>13.1751231785641</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8406525088798</v>
+        <v>43.85504223865388</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84397924642764</v>
+        <v>99.84354647804423</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.51779803731405</v>
+        <v>84.74477535306811</v>
       </c>
       <c r="C10" t="n">
-        <v>40.2485725754342</v>
+        <v>41.46363261563642</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7903425051329</v>
+        <v>1.849617489036633</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0648098464247</v>
+        <v>10.31874372416876</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520120478520158</v>
+        <v>0.752013219353299</v>
       </c>
       <c r="G10" t="n">
-        <v>27.70427776928447</v>
+        <v>28.60726285384283</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59255420119273</v>
+        <v>34.59260809025174</v>
       </c>
       <c r="I10" t="n">
-        <v>3.913726368352137</v>
+        <v>3.924447355456732</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7000752990751</v>
+        <v>4.70008262095812</v>
       </c>
       <c r="K10" t="n">
-        <v>16.48220196268595</v>
+        <v>15.25522464693188</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13897137742925</v>
+        <v>43.15052944469541</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8697459155494</v>
+        <v>99.86938670726371</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.03383952899452</v>
+        <v>82.56424953427785</v>
       </c>
       <c r="C11" t="n">
-        <v>38.37105676709014</v>
+        <v>39.89217360031358</v>
       </c>
       <c r="D11" t="n">
-        <v>1.680180030208166</v>
+        <v>1.75302153132538</v>
       </c>
       <c r="E11" t="n">
-        <v>9.989810256180332</v>
+        <v>10.32563184265027</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530222990579419</v>
+        <v>0.7530074410511287</v>
       </c>
       <c r="G11" t="n">
-        <v>25.99959176852391</v>
+        <v>27.11325343338488</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63902575666533</v>
+        <v>34.63834228835191</v>
       </c>
       <c r="I11" t="n">
-        <v>3.265820049246698</v>
+        <v>3.274696490944715</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706389369112138</v>
+        <v>4.706296506569555</v>
       </c>
       <c r="K11" t="n">
-        <v>18.96616047100547</v>
+        <v>17.43575046572215</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55406814056128</v>
+        <v>42.56306350742381</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8912853786569</v>
+        <v>99.89098757345954</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.56254274300828</v>
+        <v>80.22411182048407</v>
       </c>
       <c r="C12" t="n">
-        <v>36.40489368593504</v>
+        <v>38.05959549169354</v>
       </c>
       <c r="D12" t="n">
-        <v>1.571767480457477</v>
+        <v>1.650220246404882</v>
       </c>
       <c r="E12" t="n">
-        <v>9.799334577075989</v>
+        <v>10.17544787642252</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538928292363833</v>
+        <v>0.7538622235411035</v>
       </c>
       <c r="G12" t="n">
-        <v>24.32198461606092</v>
+        <v>25.52326880312211</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67907014487363</v>
+        <v>34.67766228289075</v>
       </c>
       <c r="I12" t="n">
-        <v>2.724662912576478</v>
+        <v>2.73201149097079</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711830182727397</v>
+        <v>4.711638897131898</v>
       </c>
       <c r="K12" t="n">
-        <v>21.43745725699172</v>
+        <v>19.77588817951593</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06693183348305</v>
+        <v>42.07355253737539</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90928277640981</v>
+        <v>99.90903620858487</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.19618317666864</v>
+        <v>77.81267069429407</v>
       </c>
       <c r="C13" t="n">
-        <v>34.45904534101565</v>
+        <v>36.07080406371325</v>
       </c>
       <c r="D13" t="n">
-        <v>1.469022520044853</v>
+        <v>1.545180451222467</v>
       </c>
       <c r="E13" t="n">
-        <v>9.537562966929041</v>
+        <v>9.907576883962834</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754642409719982</v>
+        <v>0.7545981686890001</v>
       </c>
       <c r="G13" t="n">
-        <v>22.73207938032828</v>
+        <v>23.89866206756284</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71355084711917</v>
+        <v>34.71151575969399</v>
       </c>
       <c r="I13" t="n">
-        <v>2.272809991777439</v>
+        <v>2.278898808856702</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716515060749888</v>
+        <v>4.716238554306251</v>
       </c>
       <c r="K13" t="n">
-        <v>23.80381682333135</v>
+        <v>22.18732930570592</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6614527547481</v>
+        <v>41.66597742249831</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92431491909508</v>
+        <v>99.92411079191747</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.39921573485492</v>
+        <v>84.3580789001157</v>
       </c>
       <c r="C14" t="n">
-        <v>38.83053915133439</v>
+        <v>40.06309112923356</v>
       </c>
       <c r="D14" t="n">
-        <v>1.470860413422237</v>
+        <v>1.547039247236953</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98167629698089</v>
+        <v>12.15411149605896</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555865424805028</v>
+        <v>0.7555059229046246</v>
       </c>
       <c r="G14" t="n">
-        <v>24.67099676754751</v>
+        <v>25.65462890793433</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66745824760209</v>
+        <v>36.48049007070249</v>
       </c>
       <c r="I14" t="n">
-        <v>3.13022157631853</v>
+        <v>3.04439123712445</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722415890503144</v>
+        <v>4.721912018153905</v>
       </c>
       <c r="K14" t="n">
-        <v>16.6007842651451</v>
+        <v>15.64192109988428</v>
       </c>
       <c r="L14" t="n">
-        <v>44.46446624181891</v>
+        <v>44.19362999270729</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8957896582984</v>
+        <v>99.89864222182513</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.68952013693192</v>
+        <v>83.60387086128218</v>
       </c>
       <c r="C15" t="n">
-        <v>38.59344691681166</v>
+        <v>39.77990965156862</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4437555022538</v>
+        <v>1.518928444018097</v>
       </c>
       <c r="E15" t="n">
-        <v>12.2068312496407</v>
+        <v>12.35652289702944</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563819015485238</v>
+        <v>0.7562709009426571</v>
       </c>
       <c r="G15" t="n">
-        <v>24.22710319015823</v>
+        <v>25.18846605772108</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71679760337148</v>
+        <v>36.51742793296764</v>
       </c>
       <c r="I15" t="n">
-        <v>2.611263805280918</v>
+        <v>2.53956149771166</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727386884678275</v>
+        <v>4.726693130891608</v>
       </c>
       <c r="K15" t="n">
-        <v>17.31047986306807</v>
+        <v>16.39612913871781</v>
       </c>
       <c r="L15" t="n">
-        <v>44.00912262077809</v>
+        <v>43.73939478646011</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91304940065783</v>
+        <v>99.91543357674655</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.18033990198681</v>
+        <v>81.13681742032631</v>
       </c>
       <c r="C16" t="n">
-        <v>36.48756713716737</v>
+        <v>37.70585173343756</v>
       </c>
       <c r="D16" t="n">
-        <v>1.34933563675584</v>
+        <v>1.424239904353707</v>
       </c>
       <c r="E16" t="n">
-        <v>11.77152315407358</v>
+        <v>11.9392529397352</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570667816462823</v>
+        <v>0.7569290032465679</v>
       </c>
       <c r="G16" t="n">
-        <v>22.64267991277577</v>
+        <v>23.61824128723594</v>
       </c>
       <c r="H16" t="n">
-        <v>36.75004351245589</v>
+        <v>36.54920517499245</v>
       </c>
       <c r="I16" t="n">
-        <v>2.17802351899019</v>
+        <v>2.118142840471394</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731667385289265</v>
+        <v>4.730806270291049</v>
       </c>
       <c r="K16" t="n">
-        <v>19.8196600980132</v>
+        <v>18.8631825796737</v>
       </c>
       <c r="L16" t="n">
-        <v>43.62023765911718</v>
+        <v>43.36042231195229</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92746489429774</v>
+        <v>99.92945662506355</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.00414242964314</v>
+        <v>82.71349441586963</v>
       </c>
       <c r="C17" t="n">
-        <v>37.79710201269963</v>
+        <v>38.85270414822429</v>
       </c>
       <c r="D17" t="n">
-        <v>1.350541690611811</v>
+        <v>1.425463656781597</v>
       </c>
       <c r="E17" t="n">
-        <v>12.60410437394624</v>
+        <v>12.68468583633972</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577434578463027</v>
+        <v>0.757579380828766</v>
       </c>
       <c r="G17" t="n">
-        <v>23.11849603486729</v>
+        <v>24.01835875895692</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23846898080902</v>
+        <v>36.96043334400834</v>
       </c>
       <c r="I17" t="n">
-        <v>2.198891280023093</v>
+        <v>2.132102308774508</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735896611539393</v>
+        <v>4.734871130179788</v>
       </c>
       <c r="K17" t="n">
-        <v>17.99585757035686</v>
+        <v>17.28650558413037</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13380949569882</v>
+        <v>43.78978120394234</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92676907875531</v>
+        <v>99.928990936297</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.64084990354907</v>
+        <v>80.45124336349666</v>
       </c>
       <c r="C18" t="n">
-        <v>35.77299459784746</v>
+        <v>36.91996190119717</v>
       </c>
       <c r="D18" t="n">
-        <v>1.265419549394667</v>
+        <v>1.341875494602365</v>
       </c>
       <c r="E18" t="n">
-        <v>12.11532699449256</v>
+        <v>12.23720847188377</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583250529937923</v>
+        <v>0.7581374920488132</v>
       </c>
       <c r="G18" t="n">
-        <v>21.66138005104565</v>
+        <v>22.60993949995207</v>
       </c>
       <c r="H18" t="n">
-        <v>37.2670508347794</v>
+        <v>36.98766221674315</v>
       </c>
       <c r="I18" t="n">
-        <v>1.833815839631794</v>
+        <v>1.7780608629614</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739531581211202</v>
+        <v>4.738359325305083</v>
       </c>
       <c r="K18" t="n">
-        <v>20.35915009645091</v>
+        <v>19.54875663650334</v>
       </c>
       <c r="L18" t="n">
-        <v>43.80677499236766</v>
+        <v>43.47205639816689</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93891968666603</v>
+        <v>99.9407749358674</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.70043377765107</v>
+        <v>79.56101418023974</v>
       </c>
       <c r="C19" t="n">
-        <v>35.11473216642196</v>
+        <v>36.30388467286362</v>
       </c>
       <c r="D19" t="n">
-        <v>1.232257411333798</v>
+        <v>1.309679162510125</v>
       </c>
       <c r="E19" t="n">
-        <v>12.0526890425192</v>
+        <v>12.19070092206793</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588162013418156</v>
+        <v>0.7586084275975735</v>
       </c>
       <c r="G19" t="n">
-        <v>21.09371245322376</v>
+        <v>22.06744720193032</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29118778025014</v>
+        <v>37.01063800304325</v>
       </c>
       <c r="I19" t="n">
-        <v>1.529169630595999</v>
+        <v>1.482637790605715</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742601258386348</v>
+        <v>4.741302672484835</v>
       </c>
       <c r="K19" t="n">
-        <v>21.29956622234893</v>
+        <v>20.43898581976026</v>
       </c>
       <c r="L19" t="n">
-        <v>43.53476228235044</v>
+        <v>43.20773892784941</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94906067112133</v>
+        <v>99.95060942047328</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.03162136599543</v>
+        <v>77.0732164102931</v>
       </c>
       <c r="C20" t="n">
-        <v>32.68104736767903</v>
+        <v>34.04455985952123</v>
       </c>
       <c r="D20" t="n">
-        <v>1.137232714706666</v>
+        <v>1.218724659649775</v>
       </c>
       <c r="E20" t="n">
-        <v>11.33575747206024</v>
+        <v>11.55011402385091</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592403696369396</v>
+        <v>0.7590140097854232</v>
       </c>
       <c r="G20" t="n">
-        <v>19.46708508773041</v>
+        <v>20.53490873976091</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31203306467597</v>
+        <v>37.03042535972016</v>
       </c>
       <c r="I20" t="n">
-        <v>1.275020346954328</v>
+        <v>1.23619205636703</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745252310230874</v>
+        <v>4.743837561158895</v>
       </c>
       <c r="K20" t="n">
-        <v>23.96837863400459</v>
+        <v>22.92678358970689</v>
       </c>
       <c r="L20" t="n">
-        <v>43.30809706413316</v>
+        <v>42.98747216769951</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95752306581676</v>
+        <v>99.95881561692764</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.05056927857699</v>
+        <v>82.76415259740877</v>
       </c>
       <c r="C21" t="n">
-        <v>36.36058322694336</v>
+        <v>37.50570793792956</v>
       </c>
       <c r="D21" t="n">
-        <v>1.138109773284347</v>
+        <v>1.219636090300852</v>
       </c>
       <c r="E21" t="n">
-        <v>13.33474342471751</v>
+        <v>13.4362517011582</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598259123056478</v>
+        <v>0.7595816430302564</v>
       </c>
       <c r="G21" t="n">
-        <v>21.15594618840908</v>
+        <v>22.11828737529519</v>
       </c>
       <c r="H21" t="n">
-        <v>39.01465657694291</v>
+        <v>38.62614026771249</v>
       </c>
       <c r="I21" t="n">
-        <v>1.898375451007176</v>
+        <v>1.856870250972678</v>
       </c>
       <c r="J21" t="n">
-        <v>4.7489119519103</v>
+        <v>4.747385268939103</v>
       </c>
       <c r="K21" t="n">
-        <v>17.94943072142303</v>
+        <v>17.23584740259124</v>
       </c>
       <c r="L21" t="n">
-        <v>45.62675563460478</v>
+        <v>45.19659523891223</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93676958297118</v>
+        <v>99.93815057943301</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_49_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.85881456544389</v>
+        <v>45.09177659700686</v>
       </c>
       <c r="M2" t="n">
-        <v>99.45923692991565</v>
+        <v>101.123888536213</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08764180500764</v>
+        <v>88.05651058530597</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9474759061165</v>
+        <v>45.8964356610958</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228871043394151</v>
+        <v>2.2288299544861</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720412868079844</v>
+        <v>5.689701443073494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742957014464717</v>
+        <v>0.7429433181620335</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97900847580858</v>
+        <v>33.96158803660936</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17602266537698</v>
+        <v>34.17539263545353</v>
       </c>
       <c r="I3" t="n">
-        <v>6.596888397478887</v>
+        <v>6.614659459008728</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643481340404481</v>
+        <v>4.643395738512709</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91235819499237</v>
+        <v>11.94348941469403</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90338635376561</v>
+        <v>48.92265315246146</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632204548745</v>
+        <v>106.7625782282513</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.26117723120441</v>
+        <v>87.22078288825259</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76101932759391</v>
+        <v>42.70603775791771</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189534899414106</v>
+        <v>2.188964428709849</v>
       </c>
       <c r="E4" t="n">
-        <v>6.537619008530484</v>
+        <v>6.508575864962537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445204940876701</v>
+        <v>0.7445117171238848</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37933126538182</v>
+        <v>33.35414081500737</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24794272803282</v>
+        <v>34.24753898769869</v>
       </c>
       <c r="I4" t="n">
-        <v>5.508975747709568</v>
+        <v>5.523852842725968</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653253088047938</v>
+        <v>4.653198232024279</v>
       </c>
       <c r="K4" t="n">
-        <v>12.73882276879558</v>
+        <v>12.77921711174741</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31691100368053</v>
+        <v>44.33100458980685</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81675310007003</v>
+        <v>99.81625945947198</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.32647350652876</v>
+        <v>86.28294855674204</v>
       </c>
       <c r="C5" t="n">
-        <v>42.68143746325364</v>
+        <v>42.62556027800503</v>
       </c>
       <c r="D5" t="n">
-        <v>2.144732228976668</v>
+        <v>2.143958948108431</v>
       </c>
       <c r="E5" t="n">
-        <v>7.170339282983747</v>
+        <v>7.143326998618327</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458426161555698</v>
+        <v>0.7458380702618722</v>
       </c>
       <c r="G5" t="n">
-        <v>32.69631717937427</v>
+        <v>32.668374012341</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3087603431562</v>
+        <v>34.30855123204611</v>
       </c>
       <c r="I5" t="n">
-        <v>4.598965504909997</v>
+        <v>4.611411356229594</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661516350972311</v>
+        <v>4.6614879391367</v>
       </c>
       <c r="K5" t="n">
-        <v>13.67352649347123</v>
+        <v>13.71705144325796</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49200893917207</v>
+        <v>43.50394792199461</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84697289589694</v>
+        <v>99.84655964325759</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.08142631902373</v>
+        <v>85.02333429349164</v>
       </c>
       <c r="C6" t="n">
-        <v>42.15092932900049</v>
+        <v>42.08235756555558</v>
       </c>
       <c r="D6" t="n">
-        <v>2.084300623225189</v>
+        <v>2.082729723389632</v>
       </c>
       <c r="E6" t="n">
-        <v>7.608008074057117</v>
+        <v>7.58076123504503</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469641765471093</v>
+        <v>0.7469634331097281</v>
       </c>
       <c r="G6" t="n">
-        <v>31.77504089014164</v>
+        <v>31.73539942560081</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36035212116702</v>
+        <v>34.36031792304748</v>
       </c>
       <c r="I6" t="n">
-        <v>3.83823433046622</v>
+        <v>3.848641096363163</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668526103419434</v>
+        <v>4.6685214569358</v>
       </c>
       <c r="K6" t="n">
-        <v>14.91857368097628</v>
+        <v>14.97666570650835</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80274794822018</v>
+        <v>42.81288196804081</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87225095819694</v>
+        <v>99.87190524010472</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.72810402111571</v>
+        <v>83.67939938644791</v>
       </c>
       <c r="C7" t="n">
-        <v>41.3940795675167</v>
+        <v>41.33645239570745</v>
       </c>
       <c r="D7" t="n">
-        <v>2.018848455351941</v>
+        <v>2.017695688401866</v>
       </c>
       <c r="E7" t="n">
-        <v>7.9028656916757</v>
+        <v>7.879266321630322</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479165578832186</v>
+        <v>0.7479189555661532</v>
       </c>
       <c r="G7" t="n">
-        <v>30.77722642549749</v>
+        <v>30.74444939813575</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40416166262805</v>
+        <v>34.40427195604304</v>
       </c>
       <c r="I7" t="n">
-        <v>3.202606741309198</v>
+        <v>3.211303594382318</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674478486770117</v>
+        <v>4.674493472288456</v>
       </c>
       <c r="K7" t="n">
-        <v>16.27189597888427</v>
+        <v>16.32060061355209</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2274068333083</v>
+        <v>42.23604029361925</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89338237970928</v>
+        <v>99.8930933028788</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.61238352813714</v>
+        <v>88.38674697458084</v>
       </c>
       <c r="C8" t="n">
-        <v>43.72597735250569</v>
+        <v>43.6192342239506</v>
       </c>
       <c r="D8" t="n">
-        <v>2.023125816215859</v>
+        <v>2.021893530346114</v>
       </c>
       <c r="E8" t="n">
-        <v>9.755149324209778</v>
+        <v>9.691837654428484</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495011785642238</v>
+        <v>0.7494750106148014</v>
       </c>
       <c r="G8" t="n">
-        <v>31.29084383875877</v>
+        <v>31.24677840883598</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47705421395429</v>
+        <v>34.47585048828086</v>
       </c>
       <c r="I8" t="n">
-        <v>5.632326790407827</v>
+        <v>5.516693065732099</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6843823660264</v>
+        <v>4.684218816342507</v>
       </c>
       <c r="K8" t="n">
-        <v>11.38761647186286</v>
+        <v>11.61325302541916</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69905888446263</v>
+        <v>44.58400477249156</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81265270883117</v>
+        <v>99.81649202186132</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.82487682143591</v>
+        <v>86.40504792828557</v>
       </c>
       <c r="C9" t="n">
-        <v>42.81338106082625</v>
+        <v>42.49449292817069</v>
       </c>
       <c r="D9" t="n">
-        <v>1.942660163645454</v>
+        <v>1.93205338562136</v>
       </c>
       <c r="E9" t="n">
-        <v>10.15083815588986</v>
+        <v>10.02876243534454</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508541753608908</v>
+        <v>0.7508065845273985</v>
       </c>
       <c r="G9" t="n">
-        <v>30.04631512542652</v>
+        <v>29.85836944847316</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53929206660097</v>
+        <v>34.53710288826032</v>
       </c>
       <c r="I9" t="n">
-        <v>4.702078538506639</v>
+        <v>4.605412032762555</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692838596005569</v>
+        <v>4.692541153296239</v>
       </c>
       <c r="K9" t="n">
-        <v>13.1751231785641</v>
+        <v>13.59495207171442</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85504223865388</v>
+        <v>43.75731352606678</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84354647804423</v>
+        <v>99.84675852595188</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.74477535306811</v>
+        <v>84.16741938245661</v>
       </c>
       <c r="C10" t="n">
-        <v>41.46363261563642</v>
+        <v>40.97200386824341</v>
       </c>
       <c r="D10" t="n">
-        <v>1.849617489036633</v>
+        <v>1.831458248881227</v>
       </c>
       <c r="E10" t="n">
-        <v>10.31874372416876</v>
+        <v>10.14721474867824</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752013219353299</v>
+        <v>0.7519494908848702</v>
       </c>
       <c r="G10" t="n">
-        <v>28.60726285384283</v>
+        <v>28.30375052341659</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59260809025174</v>
+        <v>34.58967658070402</v>
       </c>
       <c r="I10" t="n">
-        <v>3.924447355456732</v>
+        <v>3.843685471861234</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70008262095812</v>
+        <v>4.699684318030437</v>
       </c>
       <c r="K10" t="n">
-        <v>15.25522464693188</v>
+        <v>15.83258061754338</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15052944469541</v>
+        <v>43.06748740219202</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86938670726371</v>
+        <v>99.87207188797882</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.56424953427785</v>
+        <v>81.68233006363944</v>
       </c>
       <c r="C11" t="n">
-        <v>39.89217360031358</v>
+        <v>39.08312889746891</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75302153132538</v>
+        <v>1.720721759933676</v>
       </c>
       <c r="E11" t="n">
-        <v>10.32563184265027</v>
+        <v>10.06822192331123</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530074410511287</v>
+        <v>0.7529336695399625</v>
       </c>
       <c r="G11" t="n">
-        <v>27.11325343338488</v>
+        <v>26.59240495551999</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63834228835191</v>
+        <v>34.63494879883827</v>
       </c>
       <c r="I11" t="n">
-        <v>3.274696490944715</v>
+        <v>3.207263521871559</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706296506569555</v>
+        <v>4.705835434624764</v>
       </c>
       <c r="K11" t="n">
-        <v>17.43575046572215</v>
+        <v>18.31766993636057</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56306350742381</v>
+        <v>42.49243212528548</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89098757345954</v>
+        <v>99.89323095911496</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.22411182048407</v>
+        <v>79.22774751609172</v>
       </c>
       <c r="C12" t="n">
-        <v>38.05959549169354</v>
+        <v>37.12515302768377</v>
       </c>
       <c r="D12" t="n">
-        <v>1.650220246404882</v>
+        <v>1.612490557102561</v>
       </c>
       <c r="E12" t="n">
-        <v>10.17544787642252</v>
+        <v>9.880898350407859</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538622235411035</v>
+        <v>0.7537812875718364</v>
       </c>
       <c r="G12" t="n">
-        <v>25.52326880312211</v>
+        <v>24.91977661924618</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67766228289075</v>
+        <v>34.67393922830446</v>
       </c>
       <c r="I12" t="n">
-        <v>2.73201149097079</v>
+        <v>2.675728426134855</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711638897131898</v>
+        <v>4.711133047323975</v>
       </c>
       <c r="K12" t="n">
-        <v>19.77588817951593</v>
+        <v>20.77225248390826</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07355253737539</v>
+        <v>42.01350383502267</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90903620858487</v>
+        <v>99.9109093466147</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.81267069429407</v>
+        <v>76.76354081194127</v>
       </c>
       <c r="C13" t="n">
-        <v>36.07080406371325</v>
+        <v>35.07436905825224</v>
       </c>
       <c r="D13" t="n">
-        <v>1.545180451222467</v>
+        <v>1.504824698566385</v>
       </c>
       <c r="E13" t="n">
-        <v>9.907576883962834</v>
+        <v>9.593140724764348</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545981686890001</v>
+        <v>0.7545118386588359</v>
       </c>
       <c r="G13" t="n">
-        <v>23.89866206756284</v>
+        <v>23.25588523555839</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71151575969399</v>
+        <v>34.70754457830644</v>
       </c>
       <c r="I13" t="n">
-        <v>2.278898808856702</v>
+        <v>2.231934744469144</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716238554306251</v>
+        <v>4.715698991617722</v>
       </c>
       <c r="K13" t="n">
-        <v>22.18732930570592</v>
+        <v>23.23645918805875</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66597742249831</v>
+        <v>41.61484596407415</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92411079191747</v>
+        <v>99.92567421038513</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.3580789001157</v>
+        <v>83.71652641034453</v>
       </c>
       <c r="C14" t="n">
-        <v>40.06309112923356</v>
+        <v>39.45187444180573</v>
       </c>
       <c r="D14" t="n">
-        <v>1.547039247236953</v>
+        <v>1.506510361686857</v>
       </c>
       <c r="E14" t="n">
-        <v>12.15411149605896</v>
+        <v>12.01251776909722</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555059229046246</v>
+        <v>0.7553570220091615</v>
       </c>
       <c r="G14" t="n">
-        <v>25.65462890793433</v>
+        <v>25.22168219057997</v>
       </c>
       <c r="H14" t="n">
-        <v>36.48049007070249</v>
+        <v>36.68616936625811</v>
       </c>
       <c r="I14" t="n">
-        <v>3.04439123712445</v>
+        <v>2.813308313155951</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721912018153905</v>
+        <v>4.720981387557257</v>
       </c>
       <c r="K14" t="n">
-        <v>15.64192109988428</v>
+        <v>16.28347358965549</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19362999270729</v>
+        <v>44.17097995357438</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89864222182513</v>
+        <v>99.90632798503559</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.60387086128218</v>
+        <v>82.84079764067928</v>
       </c>
       <c r="C15" t="n">
-        <v>39.77990965156862</v>
+        <v>39.01107583942411</v>
       </c>
       <c r="D15" t="n">
-        <v>1.518928444018097</v>
+        <v>1.473846234388108</v>
       </c>
       <c r="E15" t="n">
-        <v>12.35652289702944</v>
+        <v>12.14316881474858</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562709009426571</v>
+        <v>0.7560702571140075</v>
       </c>
       <c r="G15" t="n">
-        <v>25.18846605772108</v>
+        <v>24.67482618566061</v>
       </c>
       <c r="H15" t="n">
-        <v>36.51742793296764</v>
+        <v>36.72080975893592</v>
       </c>
       <c r="I15" t="n">
-        <v>2.53956149771166</v>
+        <v>2.346637282869526</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726693130891608</v>
+        <v>4.725439106962545</v>
       </c>
       <c r="K15" t="n">
-        <v>16.39612913871781</v>
+        <v>17.15920235932069</v>
       </c>
       <c r="L15" t="n">
-        <v>43.73939478646011</v>
+        <v>43.75157434811199</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91543357674655</v>
+        <v>99.9218525468568</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.13681742032631</v>
+        <v>80.46722621612179</v>
       </c>
       <c r="C16" t="n">
-        <v>37.70585173343756</v>
+        <v>37.00026191219678</v>
       </c>
       <c r="D16" t="n">
-        <v>1.424239904353707</v>
+        <v>1.383608712495088</v>
       </c>
       <c r="E16" t="n">
-        <v>11.9392529397352</v>
+        <v>11.72587878654181</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569290032465679</v>
+        <v>0.7566832261565053</v>
       </c>
       <c r="G16" t="n">
-        <v>23.61824128723594</v>
+        <v>23.16408841927522</v>
       </c>
       <c r="H16" t="n">
-        <v>36.54920517499245</v>
+        <v>36.75058043088855</v>
       </c>
       <c r="I16" t="n">
-        <v>2.118142840471394</v>
+        <v>1.957116477286468</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730806270291049</v>
+        <v>4.729270163478156</v>
       </c>
       <c r="K16" t="n">
-        <v>18.8631825796737</v>
+        <v>19.5327737838782</v>
       </c>
       <c r="L16" t="n">
-        <v>43.36042231195229</v>
+        <v>43.40177993495641</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92945662506355</v>
+        <v>99.93481563103138</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.71349441586963</v>
+        <v>82.08270188093695</v>
       </c>
       <c r="C17" t="n">
-        <v>38.85270414822429</v>
+        <v>38.18761021625561</v>
       </c>
       <c r="D17" t="n">
-        <v>1.425463656781597</v>
+        <v>1.384695799492535</v>
       </c>
       <c r="E17" t="n">
-        <v>12.68468583633972</v>
+        <v>12.47545069920931</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757579380828766</v>
+        <v>0.7572777443095871</v>
       </c>
       <c r="G17" t="n">
-        <v>24.01835875895692</v>
+        <v>23.60018958203526</v>
       </c>
       <c r="H17" t="n">
-        <v>36.96043334400834</v>
+        <v>37.19735635933441</v>
       </c>
       <c r="I17" t="n">
-        <v>2.132102308774508</v>
+        <v>1.934745794620942</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734871130179788</v>
+        <v>4.732985901934917</v>
       </c>
       <c r="K17" t="n">
-        <v>17.28650558413037</v>
+        <v>17.91729811906303</v>
       </c>
       <c r="L17" t="n">
-        <v>43.78978120394234</v>
+        <v>43.83065076873675</v>
       </c>
       <c r="M17" t="n">
-        <v>99.928990936297</v>
+        <v>99.9355591040554</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.45124336349666</v>
+        <v>79.73372323637082</v>
       </c>
       <c r="C18" t="n">
-        <v>36.91996190119717</v>
+        <v>36.13734987417792</v>
       </c>
       <c r="D18" t="n">
-        <v>1.341875494602365</v>
+        <v>1.298742796269234</v>
       </c>
       <c r="E18" t="n">
-        <v>12.23720847188377</v>
+        <v>11.96995095045185</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581374920488132</v>
+        <v>0.7577885166675766</v>
       </c>
       <c r="G18" t="n">
-        <v>22.60993949995207</v>
+        <v>22.13524170542684</v>
       </c>
       <c r="H18" t="n">
-        <v>36.98766221674315</v>
+        <v>37.22244541227622</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7780608629614</v>
+        <v>1.613375626106762</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738359325305083</v>
+        <v>4.736178229172352</v>
       </c>
       <c r="K18" t="n">
-        <v>19.54875663650334</v>
+        <v>20.26627676362916</v>
       </c>
       <c r="L18" t="n">
-        <v>43.47205639816689</v>
+        <v>43.54263042345345</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9407749358674</v>
+        <v>99.94625706126054</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.56101418023974</v>
+        <v>78.79518224858793</v>
       </c>
       <c r="C19" t="n">
-        <v>36.30388467286362</v>
+        <v>35.44670496915772</v>
       </c>
       <c r="D19" t="n">
-        <v>1.309679162510125</v>
+        <v>1.265009774634085</v>
       </c>
       <c r="E19" t="n">
-        <v>12.19070092206793</v>
+        <v>11.88334583727539</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586084275975735</v>
+        <v>0.7582199392867445</v>
       </c>
       <c r="G19" t="n">
-        <v>22.06744720193032</v>
+        <v>21.56030986403888</v>
       </c>
       <c r="H19" t="n">
-        <v>37.01063800304325</v>
+        <v>37.24363681929597</v>
       </c>
       <c r="I19" t="n">
-        <v>1.482637790605715</v>
+        <v>1.345785393514717</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741302672484835</v>
+        <v>4.738874620542151</v>
       </c>
       <c r="K19" t="n">
-        <v>20.43898581976026</v>
+        <v>21.20481775141207</v>
       </c>
       <c r="L19" t="n">
-        <v>43.20773892784941</v>
+        <v>43.30364329110821</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95060942047328</v>
+        <v>99.95516601167799</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.0732164102931</v>
+        <v>76.38194821677887</v>
       </c>
       <c r="C20" t="n">
-        <v>34.04455985952123</v>
+        <v>33.24056602141417</v>
       </c>
       <c r="D20" t="n">
-        <v>1.218724659649775</v>
+        <v>1.177632170681737</v>
       </c>
       <c r="E20" t="n">
-        <v>11.55011402385091</v>
+        <v>11.24953756281835</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590140097854232</v>
+        <v>0.758591209736528</v>
       </c>
       <c r="G20" t="n">
-        <v>20.53490873976091</v>
+        <v>20.07108167452958</v>
       </c>
       <c r="H20" t="n">
-        <v>37.03042535972016</v>
+        <v>37.26187356179906</v>
       </c>
       <c r="I20" t="n">
-        <v>1.23619205636703</v>
+        <v>1.122036976360314</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743837561158895</v>
+        <v>4.741195060853298</v>
       </c>
       <c r="K20" t="n">
-        <v>22.92678358970689</v>
+        <v>23.61805178322115</v>
       </c>
       <c r="L20" t="n">
-        <v>42.98747216769951</v>
+        <v>43.10399926776705</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95881561692764</v>
+        <v>99.96261707240237</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.76415259740877</v>
+        <v>82.27638106803079</v>
       </c>
       <c r="C21" t="n">
-        <v>37.50570793792956</v>
+        <v>36.9436476970609</v>
       </c>
       <c r="D21" t="n">
-        <v>1.219636090300852</v>
+        <v>1.178379067162554</v>
       </c>
       <c r="E21" t="n">
-        <v>13.4362517011582</v>
+        <v>13.23170067952834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595816430302564</v>
+        <v>0.7590723354386247</v>
       </c>
       <c r="G21" t="n">
-        <v>22.11828737529519</v>
+        <v>21.79792659885016</v>
       </c>
       <c r="H21" t="n">
-        <v>38.62614026771249</v>
+        <v>38.9996215017494</v>
       </c>
       <c r="I21" t="n">
-        <v>1.856870250972678</v>
+        <v>1.565478788810292</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747385268939103</v>
+        <v>4.744202096491402</v>
       </c>
       <c r="K21" t="n">
-        <v>17.23584740259124</v>
+        <v>17.72361893196922</v>
       </c>
       <c r="L21" t="n">
-        <v>45.19659523891223</v>
+        <v>45.28058381978849</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93815057943301</v>
+        <v>99.94785044881861</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_49_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.09177659700686</v>
+        <v>43.35248890165638</v>
       </c>
       <c r="M2" t="n">
-        <v>101.123888536213</v>
+        <v>97.60004751844218</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05651058530597</v>
+        <v>81.5842249878082</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8964356610958</v>
+        <v>43.33978054336375</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2288299544861</v>
+        <v>2.185704769886953</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689701443073494</v>
+        <v>4.165106897792803</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429433181620335</v>
+        <v>0.7377086340739424</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96158803660936</v>
+        <v>32.87664258038292</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17539263545353</v>
+        <v>33.93459716740134</v>
       </c>
       <c r="I3" t="n">
-        <v>6.614659459008728</v>
+        <v>3.073785975308093</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643395738512709</v>
+        <v>4.610678962962139</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94348941469403</v>
+        <v>18.4157750121918</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92265315246146</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7625782282513</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22078288825259</v>
+        <v>88.72844905567572</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70603775791771</v>
+        <v>42.8961406270156</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188964428709849</v>
+        <v>2.191510671877255</v>
       </c>
       <c r="E4" t="n">
-        <v>6.508575864962537</v>
+        <v>6.528162852631318</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445117171238848</v>
+        <v>0.7396682143822445</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35414081500737</v>
+        <v>33.55074418928068</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24753898769869</v>
+        <v>34.02473786158324</v>
       </c>
       <c r="I4" t="n">
-        <v>5.523852842725968</v>
+        <v>7.070698926031945</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653198232024279</v>
+        <v>4.622926339889028</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77921711174741</v>
+        <v>11.27155094432428</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33100458980685</v>
+        <v>45.59724287065056</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81625945947198</v>
+        <v>99.76493444199045</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.28294855674204</v>
+        <v>87.76721433500508</v>
       </c>
       <c r="C5" t="n">
-        <v>42.62556027800503</v>
+        <v>43.03089272500529</v>
       </c>
       <c r="D5" t="n">
-        <v>2.143958948108431</v>
+        <v>2.146478897822679</v>
       </c>
       <c r="E5" t="n">
-        <v>7.143326998618327</v>
+        <v>7.378264427675279</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458380702618722</v>
+        <v>0.7413271802605315</v>
       </c>
       <c r="G5" t="n">
-        <v>32.668374012341</v>
+        <v>32.86133411654744</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30855123204611</v>
+        <v>34.10105029198444</v>
       </c>
       <c r="I5" t="n">
-        <v>4.611411356229594</v>
+        <v>5.905464544086376</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6614879391367</v>
+        <v>4.633294876628321</v>
       </c>
       <c r="K5" t="n">
-        <v>13.71705144325796</v>
+        <v>12.23278566499493</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50394792199461</v>
+        <v>44.53991330649889</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84655964325759</v>
+        <v>99.8035916964991</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.02333429349164</v>
+        <v>86.63664001505651</v>
       </c>
       <c r="C6" t="n">
-        <v>42.08235756555558</v>
+        <v>42.81703371125827</v>
       </c>
       <c r="D6" t="n">
-        <v>2.082729723389632</v>
+        <v>2.093188648316427</v>
       </c>
       <c r="E6" t="n">
-        <v>7.58076123504503</v>
+        <v>8.016844925381477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469634331097281</v>
+        <v>0.7427334964463491</v>
       </c>
       <c r="G6" t="n">
-        <v>31.73539942560081</v>
+        <v>32.0454916240098</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36031792304748</v>
+        <v>34.16574083653205</v>
       </c>
       <c r="I6" t="n">
-        <v>3.848641096363163</v>
+        <v>4.930556131580729</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6685214569358</v>
+        <v>4.642084352789682</v>
       </c>
       <c r="K6" t="n">
-        <v>14.97666570650835</v>
+        <v>13.36335998494348</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81288196804081</v>
+        <v>43.65556562201807</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87190524010472</v>
+        <v>99.83595931821982</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.67939938644791</v>
+        <v>85.27617616942294</v>
       </c>
       <c r="C7" t="n">
-        <v>41.33645239570745</v>
+        <v>42.22259431124002</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017695688401866</v>
+        <v>2.028894790810568</v>
       </c>
       <c r="E7" t="n">
-        <v>7.879266321630322</v>
+        <v>8.456502598390585</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479189555661532</v>
+        <v>0.7439283007246884</v>
       </c>
       <c r="G7" t="n">
-        <v>30.74444939813575</v>
+        <v>31.06119034097139</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40427195604304</v>
+        <v>34.22070183333566</v>
       </c>
       <c r="I7" t="n">
-        <v>3.211303594382318</v>
+        <v>4.115406425660757</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674493472288456</v>
+        <v>4.649551879529302</v>
       </c>
       <c r="K7" t="n">
-        <v>16.32060061355209</v>
+        <v>14.72382383057705</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23604029361925</v>
+        <v>42.91662196563901</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8930933028788</v>
+        <v>99.86304010745607</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.38674697458084</v>
+        <v>83.64995183121549</v>
       </c>
       <c r="C8" t="n">
-        <v>43.6192342239506</v>
+        <v>41.23587591847598</v>
       </c>
       <c r="D8" t="n">
-        <v>2.021893530346114</v>
+        <v>1.952147233508368</v>
       </c>
       <c r="E8" t="n">
-        <v>9.691837654428484</v>
+        <v>8.70898259266448</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494750106148014</v>
+        <v>0.7449463517202454</v>
       </c>
       <c r="G8" t="n">
-        <v>31.24677840883598</v>
+        <v>29.88623021175944</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47585048828086</v>
+        <v>34.26753217913128</v>
       </c>
       <c r="I8" t="n">
-        <v>5.516693065732099</v>
+        <v>3.434198564180141</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684218816342507</v>
+        <v>4.655914698251533</v>
       </c>
       <c r="K8" t="n">
-        <v>11.61325302541916</v>
+        <v>16.35004816878453</v>
       </c>
       <c r="L8" t="n">
-        <v>44.58400477249156</v>
+        <v>42.29975906758226</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81649202186132</v>
+        <v>99.88568315484275</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.40504792828557</v>
+        <v>81.93319533604843</v>
       </c>
       <c r="C9" t="n">
-        <v>42.49449292817069</v>
+        <v>40.05252191728831</v>
       </c>
       <c r="D9" t="n">
-        <v>1.93205338562136</v>
+        <v>1.871673401205155</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02876243534454</v>
+        <v>8.827498126557241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508065845273985</v>
+        <v>0.7458146999999282</v>
       </c>
       <c r="G9" t="n">
-        <v>29.85836944847316</v>
+        <v>28.65422299583136</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53710288826032</v>
+        <v>34.30747619999669</v>
       </c>
       <c r="I9" t="n">
-        <v>4.605412032762555</v>
+        <v>2.865168037458498</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692541153296239</v>
+        <v>4.66134187499955</v>
       </c>
       <c r="K9" t="n">
-        <v>13.59495207171442</v>
+        <v>18.06680466395155</v>
       </c>
       <c r="L9" t="n">
-        <v>43.75731352606678</v>
+        <v>41.7852790141996</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84675852595188</v>
+        <v>99.90460559543948</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.16741938245661</v>
+        <v>86.33519114926722</v>
       </c>
       <c r="C10" t="n">
-        <v>40.97200386824341</v>
+        <v>43.07907254140814</v>
       </c>
       <c r="D10" t="n">
-        <v>1.831458248881227</v>
+        <v>1.873803702916088</v>
       </c>
       <c r="E10" t="n">
-        <v>10.14721474867824</v>
+        <v>10.57483540524919</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519494908848702</v>
+        <v>0.7466635715661031</v>
       </c>
       <c r="G10" t="n">
-        <v>28.30375052341659</v>
+        <v>29.93280161149019</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58967658070402</v>
+        <v>35.59248923683467</v>
       </c>
       <c r="I10" t="n">
-        <v>3.843685471861234</v>
+        <v>2.947950298922839</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699684318030437</v>
+        <v>4.666647322288143</v>
       </c>
       <c r="K10" t="n">
-        <v>15.83258061754338</v>
+        <v>13.66480885073276</v>
       </c>
       <c r="L10" t="n">
-        <v>43.06748740219202</v>
+        <v>43.15796531403607</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87207188797882</v>
+        <v>99.90184670617697</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.68233006363944</v>
+        <v>86.13480662535342</v>
       </c>
       <c r="C11" t="n">
-        <v>39.08312889746891</v>
+        <v>43.2435345752555</v>
       </c>
       <c r="D11" t="n">
-        <v>1.720721759933676</v>
+        <v>1.858976352499609</v>
       </c>
       <c r="E11" t="n">
-        <v>10.06822192331123</v>
+        <v>10.94675747376333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529336695399625</v>
+        <v>0.7473900945176473</v>
       </c>
       <c r="G11" t="n">
-        <v>26.59240495551999</v>
+        <v>29.73248773118152</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63494879883827</v>
+        <v>35.66366509647985</v>
       </c>
       <c r="I11" t="n">
-        <v>3.207263521871559</v>
+        <v>2.514341786176164</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705835434624764</v>
+        <v>4.671188090735295</v>
       </c>
       <c r="K11" t="n">
-        <v>18.31766993636057</v>
+        <v>13.86519337464658</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49243212528548</v>
+        <v>42.80754212860287</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89323095911496</v>
+        <v>99.91627007850495</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.22774751609172</v>
+        <v>84.37100851738066</v>
       </c>
       <c r="C12" t="n">
-        <v>37.12515302768377</v>
+        <v>41.87102768095824</v>
       </c>
       <c r="D12" t="n">
-        <v>1.612490557102561</v>
+        <v>1.783372336612533</v>
       </c>
       <c r="E12" t="n">
-        <v>9.880898350407859</v>
+        <v>10.85105955801259</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537812875718364</v>
+        <v>0.7480093011079713</v>
       </c>
       <c r="G12" t="n">
-        <v>24.91977661924618</v>
+        <v>28.52327628975142</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67393922830446</v>
+        <v>35.69321215179252</v>
       </c>
       <c r="I12" t="n">
-        <v>2.675728426134855</v>
+        <v>2.097020748178818</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711133047323975</v>
+        <v>4.675058131924819</v>
       </c>
       <c r="K12" t="n">
-        <v>20.77225248390826</v>
+        <v>15.62899148261935</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01350383502267</v>
+        <v>42.43013800902862</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9109093466147</v>
+        <v>99.9301571726062</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.76354081194127</v>
+        <v>85.4826119904682</v>
       </c>
       <c r="C13" t="n">
-        <v>35.07436905825224</v>
+        <v>42.81952412991618</v>
       </c>
       <c r="D13" t="n">
-        <v>1.504824698566385</v>
+        <v>1.784718731283191</v>
       </c>
       <c r="E13" t="n">
-        <v>9.593140724764348</v>
+        <v>11.47784233152584</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545118386588359</v>
+        <v>0.7485740265530948</v>
       </c>
       <c r="G13" t="n">
-        <v>23.25588523555839</v>
+        <v>28.84071654609232</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70754457830644</v>
+        <v>36.01606550288398</v>
       </c>
       <c r="I13" t="n">
-        <v>2.231934744469144</v>
+        <v>1.936107186172933</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715698991617722</v>
+        <v>4.678587665956842</v>
       </c>
       <c r="K13" t="n">
-        <v>23.23645918805875</v>
+        <v>14.51738800953182</v>
       </c>
       <c r="L13" t="n">
-        <v>41.61484596407415</v>
+        <v>42.59859964109172</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92567421038513</v>
+        <v>99.9355117805397</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.71652641034453</v>
+        <v>83.64372000059757</v>
       </c>
       <c r="C14" t="n">
-        <v>39.45187444180573</v>
+        <v>41.28186342144119</v>
       </c>
       <c r="D14" t="n">
-        <v>1.506510361686857</v>
+        <v>1.707867927247305</v>
       </c>
       <c r="E14" t="n">
-        <v>12.01251776909722</v>
+        <v>11.25267798161071</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553570220091615</v>
+        <v>0.7490556500213397</v>
       </c>
       <c r="G14" t="n">
-        <v>25.22168219057997</v>
+        <v>27.59882211382808</v>
       </c>
       <c r="H14" t="n">
-        <v>36.68616936625811</v>
+        <v>36.03923780350454</v>
       </c>
       <c r="I14" t="n">
-        <v>2.813308313155951</v>
+        <v>1.614460711752211</v>
       </c>
       <c r="J14" t="n">
-        <v>4.720981387557257</v>
+        <v>4.681597812633372</v>
       </c>
       <c r="K14" t="n">
-        <v>16.28347358965549</v>
+        <v>16.35627999940243</v>
       </c>
       <c r="L14" t="n">
-        <v>44.17097995357438</v>
+        <v>42.30807582398493</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90632798503559</v>
+        <v>99.94621924482854</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.84079764067928</v>
+        <v>82.84897559905571</v>
       </c>
       <c r="C15" t="n">
-        <v>39.01107583942411</v>
+        <v>40.71740067061849</v>
       </c>
       <c r="D15" t="n">
-        <v>1.473846234388108</v>
+        <v>1.674319734391443</v>
       </c>
       <c r="E15" t="n">
-        <v>12.14316881474858</v>
+        <v>11.25930170031997</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560702571140075</v>
+        <v>0.7494673213615933</v>
       </c>
       <c r="G15" t="n">
-        <v>24.67482618566061</v>
+        <v>27.05668967366823</v>
       </c>
       <c r="H15" t="n">
-        <v>36.72080975893592</v>
+        <v>36.05904450455255</v>
       </c>
       <c r="I15" t="n">
-        <v>2.346637282869526</v>
+        <v>1.365981906251953</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725439106962545</v>
+        <v>4.684170758509958</v>
       </c>
       <c r="K15" t="n">
-        <v>17.15920235932069</v>
+        <v>17.15102440094431</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75157434811199</v>
+        <v>42.08606720868561</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9218525468568</v>
+        <v>99.9544922802484</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.46722621612179</v>
+        <v>80.64569813127684</v>
       </c>
       <c r="C16" t="n">
-        <v>37.00026191219678</v>
+        <v>38.72622067116404</v>
       </c>
       <c r="D16" t="n">
-        <v>1.383608712495088</v>
+        <v>1.58281733478803</v>
       </c>
       <c r="E16" t="n">
-        <v>11.72587878654181</v>
+        <v>10.83378432166833</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7566832261565053</v>
+        <v>0.7498201130345401</v>
       </c>
       <c r="G16" t="n">
-        <v>23.16408841927522</v>
+        <v>25.57802823307703</v>
       </c>
       <c r="H16" t="n">
-        <v>36.75058043088855</v>
+        <v>36.07601833419533</v>
       </c>
       <c r="I16" t="n">
-        <v>1.957116477286468</v>
+        <v>1.138854088047705</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729270163478156</v>
+        <v>4.686375706465875</v>
       </c>
       <c r="K16" t="n">
-        <v>19.5327737838782</v>
+        <v>19.35430186872317</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40177993495641</v>
+        <v>41.88153351827246</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93481563103138</v>
+        <v>99.96205605815967</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.08270188093695</v>
+        <v>85.02995757647111</v>
       </c>
       <c r="C17" t="n">
-        <v>38.18761021625561</v>
+        <v>41.61022135429846</v>
       </c>
       <c r="D17" t="n">
-        <v>1.384695799492535</v>
+        <v>1.583617494777543</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47545069920931</v>
+        <v>12.3803339178667</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572777443095871</v>
+        <v>0.7501991688109683</v>
       </c>
       <c r="G17" t="n">
-        <v>23.60018958203526</v>
+        <v>26.91710594446457</v>
       </c>
       <c r="H17" t="n">
-        <v>37.19735635933441</v>
+        <v>37.42040308352376</v>
       </c>
       <c r="I17" t="n">
-        <v>1.934745794620942</v>
+        <v>1.289553161959022</v>
       </c>
       <c r="J17" t="n">
-        <v>4.732985901934917</v>
+        <v>4.688744805068551</v>
       </c>
       <c r="K17" t="n">
-        <v>17.91729811906303</v>
+        <v>14.97004242352889</v>
       </c>
       <c r="L17" t="n">
-        <v>43.83065076873675</v>
+        <v>43.37677283600963</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9355591040554</v>
+        <v>99.95703661383698</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.73372323637082</v>
+        <v>86.63257234636065</v>
       </c>
       <c r="C18" t="n">
-        <v>36.13734987417792</v>
+        <v>42.35026721395173</v>
       </c>
       <c r="D18" t="n">
-        <v>1.298742796269234</v>
+        <v>1.584899973316001</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96995095045185</v>
+        <v>12.98701969931981</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577885166675766</v>
+        <v>0.7508067109331932</v>
       </c>
       <c r="G18" t="n">
-        <v>22.13524170542684</v>
+        <v>27.06183781748915</v>
       </c>
       <c r="H18" t="n">
-        <v>37.22244541227622</v>
+        <v>37.45070766402591</v>
       </c>
       <c r="I18" t="n">
-        <v>1.613375626106762</v>
+        <v>2.104758537944132</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736178229172352</v>
+        <v>4.692541943332457</v>
       </c>
       <c r="K18" t="n">
-        <v>20.26627676362916</v>
+        <v>13.36742765363936</v>
       </c>
       <c r="L18" t="n">
-        <v>43.54263042345345</v>
+        <v>44.21220328583419</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94625706126054</v>
+        <v>99.92989815342527</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.79518224858793</v>
+        <v>84.22236209748064</v>
       </c>
       <c r="C19" t="n">
-        <v>35.44670496915772</v>
+        <v>40.26668152689261</v>
       </c>
       <c r="D19" t="n">
-        <v>1.265009774634085</v>
+        <v>1.494186129397309</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88334583727539</v>
+        <v>12.53622111233508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582199392867445</v>
+        <v>0.7513282683082636</v>
       </c>
       <c r="G19" t="n">
-        <v>21.56030986403888</v>
+        <v>25.51291777631301</v>
       </c>
       <c r="H19" t="n">
-        <v>37.24363681929597</v>
+        <v>37.47672327163748</v>
       </c>
       <c r="I19" t="n">
-        <v>1.345785393514717</v>
+        <v>1.75518386256285</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738874620542151</v>
+        <v>4.695801676926647</v>
       </c>
       <c r="K19" t="n">
-        <v>21.20481775141207</v>
+        <v>15.77763790251936</v>
       </c>
       <c r="L19" t="n">
-        <v>43.30364329110821</v>
+        <v>43.89721505564514</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95516601167799</v>
+        <v>99.9415344850571</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.38194821677887</v>
+        <v>81.66351524617768</v>
       </c>
       <c r="C20" t="n">
-        <v>33.24056602141417</v>
+        <v>37.97958197151775</v>
       </c>
       <c r="D20" t="n">
-        <v>1.177632170681737</v>
+        <v>1.398332248006002</v>
       </c>
       <c r="E20" t="n">
-        <v>11.24953756281835</v>
+        <v>11.97592824373298</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758591209736528</v>
+        <v>0.7517770975429708</v>
       </c>
       <c r="G20" t="n">
-        <v>20.07108167452958</v>
+        <v>23.87623266301772</v>
       </c>
       <c r="H20" t="n">
-        <v>37.26187356179906</v>
+        <v>37.49911115418477</v>
       </c>
       <c r="I20" t="n">
-        <v>1.122036976360314</v>
+        <v>1.46352698004966</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741195060853298</v>
+        <v>4.698606859643567</v>
       </c>
       <c r="K20" t="n">
-        <v>23.61805178322115</v>
+        <v>18.33648475382233</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10399926776705</v>
+        <v>43.6351781673665</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96261707240237</v>
+        <v>99.95124489270658</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.27638106803079</v>
+        <v>79.14280929318468</v>
       </c>
       <c r="C21" t="n">
-        <v>36.9436476970609</v>
+        <v>35.6848319354247</v>
       </c>
       <c r="D21" t="n">
-        <v>1.178379067162554</v>
+        <v>1.304378439621495</v>
       </c>
       <c r="E21" t="n">
-        <v>13.23170067952834</v>
+        <v>11.3746388871941</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590723354386247</v>
+        <v>0.7521634636338199</v>
       </c>
       <c r="G21" t="n">
-        <v>21.79792659885016</v>
+        <v>22.27199090161666</v>
       </c>
       <c r="H21" t="n">
-        <v>38.9996215017494</v>
+        <v>37.51838333610453</v>
       </c>
       <c r="I21" t="n">
-        <v>1.565478788810292</v>
+        <v>1.220232617302692</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744202096491402</v>
+        <v>4.701021647711373</v>
       </c>
       <c r="K21" t="n">
-        <v>17.72361893196922</v>
+        <v>20.85719070681532</v>
       </c>
       <c r="L21" t="n">
-        <v>45.28058381978849</v>
+        <v>43.41732383053639</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94785044881861</v>
+        <v>99.95934647277642</v>
       </c>
     </row>
   </sheetData>
